--- a/examples/hsm_example.xlsx
+++ b/examples/hsm_example.xlsx
@@ -463,25 +463,30 @@
     </comment>
     <comment ref="K1" authorId="0" shapeId="0">
       <text>
+        <t>Distanza fra gabbia ed estremita' piu' vicina alla fermata per invertire, m (vuoto = minima distanza di frenata)</t>
+      </text>
+    </comment>
+    <comment ref="L1" authorId="0" shapeId="0">
+      <text>
         <t>Velocita' di avvicinamento dopo l'inversione (vuoto = v_ingresso)</t>
       </text>
     </comment>
-    <comment ref="L1" authorId="0" shapeId="0">
+    <comment ref="M1" authorId="0" shapeId="0">
       <text>
         <t>SI sulla gabbia che detta il bilancio di massa del gruppo tandem</t>
       </text>
     </comment>
-    <comment ref="M1" authorId="0" shapeId="0">
+    <comment ref="N1" authorId="0" shapeId="0">
       <text>
         <t>Zoom rolling: incremento di velocita' in %</t>
       </text>
     </comment>
-    <comment ref="N1" authorId="0" shapeId="0">
+    <comment ref="O1" authorId="0" shapeId="0">
       <text>
         <t>Zoom: avanzamento della testa virtuale oltre questa gabbia, m</t>
       </text>
     </comment>
-    <comment ref="O1" authorId="0" shapeId="0">
+    <comment ref="P1" authorId="0" shapeId="0">
       <text>
         <t>Zoom: accelerazione, m/s2 (vuoto = quella dell'asse)</t>
       </text>
@@ -804,7 +809,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A21"/>
+  <dimension ref="A1:A22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -892,42 +897,49 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="45" customHeight="1">
+    <row r="15" ht="75" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Dopo il tail-out il pezzo decelera fino a fermarsi, attende il reversing delay della passata successiva e riparte nel verso opposto. Il reversing delay deve gia' comprendere screwdown e centraggio sideguides.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr"/>
+          <t>Dopo il tail-out il pezzo prosegue fino a portare l'estremita' piu' vicina alla gabbia a reversing_clearance_m metri da essa, dove si ferma, attende il reversing delay della passata successiva e riparte nel verso opposto. Il reversing delay deve gia' comprendere screwdown e centraggio sideguides, e la quota di sgombero va misurata dalla gabbia, quindi va aumentata se il vincolo vero e' l'edger che sta qualche metro prima.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="45" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Lasciando vuota la quota di sgombero il pezzo si ferma appena la decelerazione lo consente, cioe' a v^2/(2a) dalla gabbia. Se la quota richiesta e' piu' corta di quella distanza il tool lo segnala invece di fingere una frenata impossibile.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
         <is>
           <t>Zoom rolling</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="60" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="19" ht="60" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>Definito come incremento percentuale di velocita' che parte quando la testa ha superato di zoom_trigger_m la gabbia indicata. Il trigger usa la testa virtuale, cioe' ignora il fatto che la testa si ferma all'avvolgitore: se il trigger cade oltre l'avvolgitore lo zoom parte dopo qualche avvolgimento, come nel modello offline.</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr"/>
-    </row>
     <row r="20">
-      <c r="A20" s="1" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
         <is>
           <t>Cosa il modello non fa</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="60" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="22" ht="60" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>Nessun interblocco e nessun hold point: i pezzi seguono i profili nominali e il tool riporta dove il gap scende sotto soglia, senza fermare il pezzo che segue. Slittamento sui rulli trascurato, jerk infinito, nessun modello termico, nessun vincolo di forno o di ciclo avvolgitore.</t>
         </is>
@@ -1929,7 +1941,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O14"/>
+  <dimension ref="A1:P14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1942,11 +1954,12 @@
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
     <col width="25" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="22" customWidth="1" min="14" max="14"/>
-    <col width="23" customWidth="1" min="15" max="15"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="23" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -2002,25 +2015,30 @@
       </c>
       <c r="K1" s="3" t="inlineStr">
         <is>
+          <t>reversing_clearance_m</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
           <t>approach_v_mps</t>
         </is>
       </c>
-      <c r="L1" s="3" t="inlineStr">
+      <c r="M1" s="3" t="inlineStr">
         <is>
           <t>master</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
+      <c r="N1" s="3" t="inlineStr">
         <is>
           <t>zoom_pct</t>
         </is>
       </c>
-      <c r="N1" s="3" t="inlineStr">
+      <c r="O1" s="3" t="inlineStr">
         <is>
           <t>zoom_trigger_m</t>
         </is>
       </c>
-      <c r="O1" s="3" t="inlineStr">
+      <c r="P1" s="3" t="inlineStr">
         <is>
           <t>zoom_accel_mps2</t>
         </is>
@@ -2063,7 +2081,7 @@
       <c r="J2" t="n">
         <v>0</v>
       </c>
-      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2102,7 +2120,10 @@
       <c r="J3" t="n">
         <v>6</v>
       </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="K3" t="n">
+        <v>5</v>
+      </c>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2141,7 +2162,10 @@
       <c r="J4" t="n">
         <v>6</v>
       </c>
-      <c r="L4" t="inlineStr"/>
+      <c r="K4" t="n">
+        <v>5</v>
+      </c>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2180,7 +2204,7 @@
       <c r="J5" t="n">
         <v>0</v>
       </c>
-      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2219,7 +2243,10 @@
       <c r="J6" t="n">
         <v>6</v>
       </c>
-      <c r="L6" t="inlineStr"/>
+      <c r="K6" t="n">
+        <v>5</v>
+      </c>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2258,7 +2285,10 @@
       <c r="J7" t="n">
         <v>6</v>
       </c>
-      <c r="L7" t="inlineStr"/>
+      <c r="K7" t="n">
+        <v>5</v>
+      </c>
+      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2297,7 +2327,7 @@
       <c r="J8" t="n">
         <v>0</v>
       </c>
-      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2336,7 +2366,7 @@
       <c r="J9" t="n">
         <v>0</v>
       </c>
-      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2375,7 +2405,7 @@
       <c r="J10" t="n">
         <v>0</v>
       </c>
-      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2414,7 +2444,7 @@
       <c r="J11" t="n">
         <v>0</v>
       </c>
-      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2453,7 +2483,7 @@
       <c r="J12" t="n">
         <v>0</v>
       </c>
-      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2492,7 +2522,7 @@
       <c r="J13" t="n">
         <v>0</v>
       </c>
-      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2531,15 +2561,15 @@
       <c r="J14" t="n">
         <v>0</v>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>8</v>
       </c>
-      <c r="N14" t="n">
+      <c r="O14" t="n">
         <v>130</v>
       </c>
     </row>

--- a/examples/hsm_example.xlsx
+++ b/examples/hsm_example.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Guida" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Guide" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Info" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Layout" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Sections" sheetId="4" state="visible" r:id="rId4"/>
@@ -163,12 +163,12 @@
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
       <text>
-        <t>Chiave</t>
+        <t>Key</t>
       </text>
     </comment>
     <comment ref="B1" authorId="0" shapeId="0">
       <text>
-        <t>Valore</t>
+        <t>Value</t>
       </text>
     </comment>
   </commentList>
@@ -183,7 +183,7 @@
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
       <text>
-        <t>Identificativo univoco (R1, F7, DC1)</t>
+        <t>Unique identifier (R1, F7, DC1)</t>
       </text>
     </comment>
     <comment ref="B1" authorId="0" shapeId="0">
@@ -193,22 +193,22 @@
     </comment>
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
-        <t>Posizione assoluta lungo la linea, in metri</t>
+        <t>Absolute position along the line, in metres</t>
       </text>
     </comment>
     <comment ref="D1" authorId="0" shapeId="0">
       <text>
-        <t>Accelerazione = decelerazione dell'asse, m/s2</t>
+        <t>Acceleration = deceleration of the axis, m/s2</t>
       </text>
     </comment>
     <comment ref="E1" authorId="0" shapeId="0">
       <text>
-        <t>Gruppo tandem, es. FM per le gabbie finitrici</t>
+        <t>Tandem group, for example FM for the finishing stands</t>
       </text>
     </comment>
     <comment ref="F1" authorId="0" shapeId="0">
       <text>
-        <t>Descrizione mostrata sui grafici</t>
+        <t>Description shown on the charts</t>
       </text>
     </comment>
   </commentList>
@@ -223,142 +223,142 @@
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
       <text>
-        <t>Identificativo univoco della sezione</t>
+        <t>Unique identifier of the section</t>
       </text>
     </comment>
     <comment ref="B1" authorId="0" shapeId="0">
       <text>
-        <t>Descrizione mostrata sui grafici</t>
+        <t>Description shown on the charts</t>
       </text>
     </comment>
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
-        <t>Apparecchiatura di riferimento, 'prev' o vuoto per assoluto</t>
+        <t>Reference equipment, 'prev', or empty for an absolute position</t>
       </text>
     </comment>
     <comment ref="D1" authorId="0" shapeId="0">
       <text>
-        <t>Distanza dal riferimento all'inizio della sezione, m</t>
+        <t>Distance from the reference to the start of the section, m</t>
       </text>
     </comment>
     <comment ref="E1" authorId="0" shapeId="0">
       <text>
-        <t>Lunghezza della sezione, m</t>
+        <t>Length of the section, m</t>
       </text>
     </comment>
     <comment ref="F1" authorId="0" shapeId="0">
       <text>
-        <t>fwd | rev: verso di moto in cui gli eventi sono validi</t>
+        <t>fwd | rev: direction of travel in which the events apply</t>
       </text>
     </comment>
     <comment ref="G1" authorId="0" shapeId="0">
       <text>
-        <t>SI se l'evento vale anche in laminazione, NO per differirlo</t>
+        <t>YES if the event applies while rolling, NO to defer it</t>
       </text>
     </comment>
     <comment ref="H1" authorId="0" shapeId="0">
       <text>
-        <t>Distanza dall'inizio sezione del cambio di velocita' 1, m</t>
+        <t>Distance from the start of the section of speed change 1, m</t>
       </text>
     </comment>
     <comment ref="I1" authorId="0" shapeId="0">
       <text>
-        <t>Nuova velocita' comandata 1, m/s</t>
+        <t>New commanded speed 1, m/s</t>
       </text>
     </comment>
     <comment ref="J1" authorId="0" shapeId="0">
       <text>
-        <t>Accelerazione del cambio 1, m/s2 (vuoto = quella dell'asse)</t>
+        <t>Acceleration of change 1, m/s2 (empty = the one of the axis)</t>
       </text>
     </comment>
     <comment ref="K1" authorId="0" shapeId="0">
       <text>
-        <t>Distanza dall'inizio sezione del cambio di velocita' 2, m</t>
+        <t>Distance from the start of the section of speed change 2, m</t>
       </text>
     </comment>
     <comment ref="L1" authorId="0" shapeId="0">
       <text>
-        <t>Nuova velocita' comandata 2, m/s</t>
+        <t>New commanded speed 2, m/s</t>
       </text>
     </comment>
     <comment ref="M1" authorId="0" shapeId="0">
       <text>
-        <t>Accelerazione del cambio 2, m/s2 (vuoto = quella dell'asse)</t>
+        <t>Acceleration of change 2, m/s2 (empty = the one of the axis)</t>
       </text>
     </comment>
     <comment ref="N1" authorId="0" shapeId="0">
       <text>
-        <t>Distanza dall'inizio sezione del cambio di velocita' 3, m</t>
+        <t>Distance from the start of the section of speed change 3, m</t>
       </text>
     </comment>
     <comment ref="O1" authorId="0" shapeId="0">
       <text>
-        <t>Nuova velocita' comandata 3, m/s</t>
+        <t>New commanded speed 3, m/s</t>
       </text>
     </comment>
     <comment ref="P1" authorId="0" shapeId="0">
       <text>
-        <t>Accelerazione del cambio 3, m/s2 (vuoto = quella dell'asse)</t>
+        <t>Acceleration of change 3, m/s2 (empty = the one of the axis)</t>
       </text>
     </comment>
     <comment ref="Q1" authorId="0" shapeId="0">
       <text>
-        <t>Distanza dall'inizio sezione del cambio di velocita' 4, m</t>
+        <t>Distance from the start of the section of speed change 4, m</t>
       </text>
     </comment>
     <comment ref="R1" authorId="0" shapeId="0">
       <text>
-        <t>Nuova velocita' comandata 4, m/s</t>
+        <t>New commanded speed 4, m/s</t>
       </text>
     </comment>
     <comment ref="S1" authorId="0" shapeId="0">
       <text>
-        <t>Accelerazione del cambio 4, m/s2 (vuoto = quella dell'asse)</t>
+        <t>Acceleration of change 4, m/s2 (empty = the one of the axis)</t>
       </text>
     </comment>
     <comment ref="T1" authorId="0" shapeId="0">
       <text>
-        <t>Distanza dall'inizio sezione del cambio di velocita' 5, m</t>
+        <t>Distance from the start of the section of speed change 5, m</t>
       </text>
     </comment>
     <comment ref="U1" authorId="0" shapeId="0">
       <text>
-        <t>Nuova velocita' comandata 5, m/s</t>
+        <t>New commanded speed 5, m/s</t>
       </text>
     </comment>
     <comment ref="V1" authorId="0" shapeId="0">
       <text>
-        <t>Accelerazione del cambio 5, m/s2 (vuoto = quella dell'asse)</t>
+        <t>Acceleration of change 5, m/s2 (empty = the one of the axis)</t>
       </text>
     </comment>
     <comment ref="W1" authorId="0" shapeId="0">
       <text>
-        <t>Distanza dall'inizio sezione del cambio di velocita' 6, m</t>
+        <t>Distance from the start of the section of speed change 6, m</t>
       </text>
     </comment>
     <comment ref="X1" authorId="0" shapeId="0">
       <text>
-        <t>Nuova velocita' comandata 6, m/s</t>
+        <t>New commanded speed 6, m/s</t>
       </text>
     </comment>
     <comment ref="Y1" authorId="0" shapeId="0">
       <text>
-        <t>Accelerazione del cambio 6, m/s2 (vuoto = quella dell'asse)</t>
+        <t>Acceleration of change 6, m/s2 (empty = the one of the axis)</t>
       </text>
     </comment>
     <comment ref="Z1" authorId="0" shapeId="0">
       <text>
-        <t>Distanza dall'inizio sezione del cambio di velocita' 7, m</t>
+        <t>Distance from the start of the section of speed change 7, m</t>
       </text>
     </comment>
     <comment ref="AA1" authorId="0" shapeId="0">
       <text>
-        <t>Nuova velocita' comandata 7, m/s</t>
+        <t>New commanded speed 7, m/s</t>
       </text>
     </comment>
     <comment ref="AB1" authorId="0" shapeId="0">
       <text>
-        <t>Accelerazione del cambio 7, m/s2 (vuoto = quella dell'asse)</t>
+        <t>Acceleration of change 7, m/s2 (empty = the one of the axis)</t>
       </text>
     </comment>
   </commentList>
@@ -373,32 +373,32 @@
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
       <text>
-        <t>Identificativo univoco del prodotto</t>
+        <t>Unique identifier of the product</t>
       </text>
     </comment>
     <comment ref="B1" authorId="0" shapeId="0">
       <text>
-        <t>Descrizione</t>
+        <t>Description</t>
       </text>
     </comment>
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
-        <t>Qualita' acciaio</t>
+        <t>Steel grade</t>
       </text>
     </comment>
     <comment ref="D1" authorId="0" shapeId="0">
       <text>
-        <t>Spessore bramma, mm</t>
+        <t>Slab thickness, mm</t>
       </text>
     </comment>
     <comment ref="E1" authorId="0" shapeId="0">
       <text>
-        <t>Larghezza bramma, mm</t>
+        <t>Slab width, mm</t>
       </text>
     </comment>
     <comment ref="F1" authorId="0" shapeId="0">
       <text>
-        <t>Lunghezza bramma, m</t>
+        <t>Slab length, m</t>
       </text>
     </comment>
   </commentList>
@@ -413,17 +413,17 @@
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
       <text>
-        <t>Prodotto a cui appartiene la passata</t>
+        <t>Product this pass belongs to</t>
       </text>
     </comment>
     <comment ref="B1" authorId="0" shapeId="0">
       <text>
-        <t>Numero d'ordine della passata</t>
+        <t>Sequence number of the pass</t>
       </text>
     </comment>
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
-        <t>Gabbia su cui avviene la passata</t>
+        <t>Stand where the pass takes place</t>
       </text>
     </comment>
     <comment ref="D1" authorId="0" shapeId="0">
@@ -433,62 +433,62 @@
     </comment>
     <comment ref="E1" authorId="0" shapeId="0">
       <text>
-        <t>Spessore in ingresso, mm</t>
+        <t>Entry thickness, mm</t>
       </text>
     </comment>
     <comment ref="F1" authorId="0" shapeId="0">
       <text>
-        <t>Spessore in uscita, mm</t>
+        <t>Exit thickness, mm</t>
       </text>
     </comment>
     <comment ref="G1" authorId="0" shapeId="0">
       <text>
-        <t>Larghezza in ingresso, mm</t>
+        <t>Entry width, mm</t>
       </text>
     </comment>
     <comment ref="H1" authorId="0" shapeId="0">
       <text>
-        <t>Larghezza in uscita, mm</t>
+        <t>Exit width, mm</t>
       </text>
     </comment>
     <comment ref="I1" authorId="0" shapeId="0">
       <text>
-        <t>Velocita' del materiale in uscita gabbia, m/s</t>
+        <t>Material speed at the stand exit, m/s</t>
       </text>
     </comment>
     <comment ref="J1" authorId="0" shapeId="0">
       <text>
-        <t>Tempo morto prima di questa passata se cambia il verso, s</t>
+        <t>Dead time ahead of this pass when the direction changes, s</t>
       </text>
     </comment>
     <comment ref="K1" authorId="0" shapeId="0">
       <text>
-        <t>Distanza fra gabbia ed estremita' piu' vicina alla fermata per invertire, m (vuoto = minima distanza di frenata)</t>
+        <t>Distance between the stand and the closest extremity when the piece stops to reverse, m (empty = shortest braking distance)</t>
       </text>
     </comment>
     <comment ref="L1" authorId="0" shapeId="0">
       <text>
-        <t>Velocita' di avvicinamento dopo l'inversione (vuoto = v_ingresso)</t>
+        <t>Approach speed after the reversal (empty = entry speed)</t>
       </text>
     </comment>
     <comment ref="M1" authorId="0" shapeId="0">
       <text>
-        <t>SI sulla gabbia che detta il bilancio di massa del gruppo tandem</t>
+        <t>YES on the stand that sets the mass flow of the tandem group</t>
       </text>
     </comment>
     <comment ref="N1" authorId="0" shapeId="0">
       <text>
-        <t>Zoom rolling: incremento di velocita' in %</t>
+        <t>Zoom rolling: speed increase in per cent</t>
       </text>
     </comment>
     <comment ref="O1" authorId="0" shapeId="0">
       <text>
-        <t>Zoom: avanzamento della testa virtuale oltre questa gabbia, m</t>
+        <t>Zoom: travel of the virtual head beyond this stand, m</t>
       </text>
     </comment>
     <comment ref="P1" authorId="0" shapeId="0">
       <text>
-        <t>Zoom: accelerazione, m/s2 (vuoto = quella dell'asse)</t>
+        <t>Zoom: acceleration, m/s2 (empty = the one of the axis)</t>
       </text>
     </comment>
   </commentList>
@@ -503,17 +503,17 @@
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
       <text>
-        <t>Chiave</t>
+        <t>Key</t>
       </text>
     </comment>
     <comment ref="B1" authorId="0" shapeId="0">
       <text>
-        <t>Valore</t>
+        <t>Value</t>
       </text>
     </comment>
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
-        <t>Descrizione</t>
+        <t>Description</t>
       </text>
     </comment>
   </commentList>
@@ -818,7 +818,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Come e' fatto il modello</t>
+          <t>How the model works</t>
         </is>
       </c>
     </row>
@@ -828,14 +828,14 @@
     <row r="3" ht="45" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>La testa comanda, la coda si deduce. Si descrivono i cambi di velocita' dell'estremita' che guida nel verso corrente; la velocita' dell'altra estremita' discende dal bilancio di massa delle gabbie ingaggiate:</t>
+          <t>The head commands, the tail follows. You describe the speed changes of the extremity that leads in the current direction of travel; the speed of the other extremity follows from the mass flow balance of the engaged stands:</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    v_trascinata = v_guida / prodotto dei lambda,   lambda = (h_in*w_in)/(h_out*w_out)</t>
+          <t xml:space="preserve">    v_trailing = v_leading / product of the lambdas,   lambda = (h_in*w_in)/(h_out*w_out)</t>
         </is>
       </c>
     </row>
@@ -845,21 +845,21 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Unita' fissate nel file, nessuna colonna unita' da compilare:</t>
+          <t>Units are fixed in the file, there is no unit column to fill in:</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    posizioni e lunghezze in m, spessori e larghezze in mm,</t>
+          <t xml:space="preserve">    positions and lengths in m, thicknesses and widths in mm,</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    velocita' in m/s, tempi in s, accelerazioni in m/s2.</t>
+          <t xml:space="preserve">    speeds in m/s, times in s, accelerations in m/s2.</t>
         </is>
       </c>
     </row>
@@ -869,21 +869,21 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Sezioni ed eventi di velocita'</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="45" customHeight="1">
+          <t>Sections and speed events</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="60" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Le vie a rulli non hanno un setpoint proprio: la linea e' divisa in sezioni definite da chi compila, anche piu' corte dell'interasse fra due gabbie. Ogni sezione ammette fino a 7 cambi di velocita', dati come distanza dall'inizio della sezione piu' velocita' obiettivo.</t>
+          <t>Roller tables have no setpoint of their own: the line is divided into sections defined by whoever fills in the file, possibly shorter than the spacing between two stands. Each section allows up to 7 speed changes, given as a distance from the start of the section plus a target speed.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="45" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Un evento che scatta mentre una passata e' ingaggiata viene differito al disingaggio, perche' in laminazione comanda il mill e non la via a rulli. Mettere SI in during_pass per farlo valere comunque.</t>
+          <t>An event that would fire while a pass is engaged is deferred to disengagement, because while rolling it is the mill that commands, not the roller table. Put YES in during_pass to make it apply anyway.</t>
         </is>
       </c>
     </row>
@@ -893,21 +893,21 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Sbozzatura reversibile</t>
+          <t>Reversing roughing</t>
         </is>
       </c>
     </row>
     <row r="15" ht="75" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Dopo il tail-out il pezzo prosegue fino a portare l'estremita' piu' vicina alla gabbia a reversing_clearance_m metri da essa, dove si ferma, attende il reversing delay della passata successiva e riparte nel verso opposto. Il reversing delay deve gia' comprendere screwdown e centraggio sideguides, e la quota di sgombero va misurata dalla gabbia, quindi va aumentata se il vincolo vero e' l'edger che sta qualche metro prima.</t>
+          <t>After tail-out the piece keeps going until the extremity closest to the stand is reversing_clearance_m metres away from it, where it stops, waits for the reversing delay of the following pass and restarts in the opposite direction. The reversing delay must already include screwdown and side guide centring, and the clearance is measured from the stand, so increase it if the real constraint is the edger a few metres before.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="45" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Lasciando vuota la quota di sgombero il pezzo si ferma appena la decelerazione lo consente, cioe' a v^2/(2a) dalla gabbia. Se la quota richiesta e' piu' corta di quella distanza il tool lo segnala invece di fingere una frenata impossibile.</t>
+          <t>Leaving the clearance empty makes the piece stop as soon as the deceleration allows, that is at v^2/(2a) from the stand. If the requested clearance is shorter than that distance the tool reports it rather than faking an impossible braking.</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
     <row r="19" ht="60" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Definito come incremento percentuale di velocita' che parte quando la testa ha superato di zoom_trigger_m la gabbia indicata. Il trigger usa la testa virtuale, cioe' ignora il fatto che la testa si ferma all'avvolgitore: se il trigger cade oltre l'avvolgitore lo zoom parte dopo qualche avvolgimento, come nel modello offline.</t>
+          <t>Defined as a percentage speed increase starting when the head has travelled zoom_trigger_m beyond the given stand. The trigger uses the virtual head, that is it ignores the fact that the head stops at the coiler: if the trigger falls beyond the coiler the zoom starts after a few wraps, as in the offline model.</t>
         </is>
       </c>
     </row>
@@ -934,14 +934,14 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>Cosa il modello non fa</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="60" customHeight="1">
+          <t>What the model does not do</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="45" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Nessun interblocco e nessun hold point: i pezzi seguono i profili nominali e il tool riporta dove il gap scende sotto soglia, senza fermare il pezzo che segue. Slittamento sui rulli trascurato, jerk infinito, nessun modello termico, nessun vincolo di forno o di ciclo avvolgitore.</t>
+          <t>No interlocks and no hold points: the pieces follow their nominal profiles and the tool reports where the gap drops below the threshold, without stopping the piece behind. Roller slip neglected, infinite jerk, no thermal model, no furnace or coiler cycle constraint.</t>
         </is>
       </c>
     </row>
@@ -995,7 +995,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HSM di esempio</t>
+          <t>Example HSM</t>
         </is>
       </c>
     </row>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Dati inventati a scopo dimostrativo</t>
+          <t>Invented data, for demonstration only</t>
         </is>
       </c>
     </row>
@@ -1086,7 +1086,7 @@
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Uscita forno</t>
+          <t>Furnace exit</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Descagliatore primario</t>
+          <t>Primary descaler</t>
         </is>
       </c>
     </row>
@@ -1158,7 +1158,7 @@
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sbozzatore R1</t>
+          <t>Roughing stand R1</t>
         </is>
       </c>
     </row>
@@ -1206,7 +1206,7 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sbozzatore R2</t>
+          <t>Roughing stand R2</t>
         </is>
       </c>
     </row>
@@ -1230,7 +1230,7 @@
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cesoia crop</t>
+          <t>Crop shear</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Descagliatore finitore</t>
+          <t>Finishing descaler</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Avvolgitore 1</t>
+          <t>Downcoiler 1</t>
         </is>
       </c>
     </row>
@@ -1673,7 +1673,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Forno - R1</t>
+          <t>Furnace to R1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1712,7 +1712,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>R1 - R2</t>
+          <t>R1 to R2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1745,7 +1745,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tavolo di trasferimento</t>
+          <t>Transfer table</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Cesoia - F1</t>
+          <t>Shear to F1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Finitore - avvolgitore</t>
+          <t>Finishing mill to coiler</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="N14" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>Cadenza nominale fra un pezzo e il successivo, s</t>
+          <t>Nominal cadence between one piece and the next, s</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Numero di pezzi simulati</t>
+          <t>Number of simulated pieces</t>
         </is>
       </c>
     </row>
@@ -2649,7 +2649,7 @@
       <c r="B4" t="inlineStr"/>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Sequenza prodotti separata da virgole (vuoto = ripete il primo)</t>
+          <t>Comma separated product sequence (empty = repeat the first)</t>
         </is>
       </c>
     </row>
@@ -2664,7 +2664,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Distanza minima ammessa fra coda e testa successiva, m</t>
+          <t>Minimum distance allowed between a tail and the next head, m</t>
         </is>
       </c>
     </row>
@@ -2679,7 +2679,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Estremo inferiore della scansione del pacing, s</t>
+          <t>Lower bound of the pacing scan, s</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Estremo superiore della scansione del pacing, s</t>
+          <t>Upper bound of the pacing scan, s</t>
         </is>
       </c>
     </row>
@@ -2709,7 +2709,7 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Numero di punti della scansione</t>
+          <t>Number of points in the scan</t>
         </is>
       </c>
     </row>
@@ -2724,7 +2724,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Numero di run Monte Carlo per la robustezza</t>
+          <t>Number of Monte Carlo runs for the robustness study</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Tolleranza sulle velocita' di passata, +/- %</t>
+          <t>Tolerance on the pass speeds, +/- %</t>
         </is>
       </c>
     </row>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Deviazione standard sui tempi morti, s</t>
+          <t>Standard deviation of the dead times, s</t>
         </is>
       </c>
     </row>
@@ -2769,7 +2769,7 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Deviazione standard sull'istante di rilascio, s</t>
+          <t>Standard deviation of the release instant, s</t>
         </is>
       </c>
     </row>
@@ -2784,7 +2784,7 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Seme del generatore casuale, per risultati riproducibili</t>
+          <t>Seed of the random generator, for reproducible results</t>
         </is>
       </c>
     </row>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Tempo massimo di simulazione di un pezzo, s</t>
+          <t>Maximum simulation time of a single piece, s</t>
         </is>
       </c>
     </row>
@@ -2811,12 +2811,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>SI per tempo crescente verso il basso nel diagramma</t>
+          <t>YES for time increasing downwards on the diagram</t>
         </is>
       </c>
     </row>

--- a/examples/hsm_example.xlsx
+++ b/examples/hsm_example.xlsx
@@ -198,7 +198,7 @@
     </comment>
     <comment ref="D1" authorId="0" shapeId="0">
       <text>
-        <t>Acceleration = deceleration of the axis, m/s2</t>
+        <t>Acceleration = deceleration, m/s2. Read only on stand rows, where it applies while the piece is gripped, and on the coiler row, where it sets the final slowdown. Ignored on start and marker rows</t>
       </text>
     </comment>
     <comment ref="E1" authorId="0" shapeId="0">
@@ -258,105 +258,110 @@
     </comment>
     <comment ref="H1" authorId="0" shapeId="0">
       <text>
+        <t>Roller table acceleration in this section, m/s2 (empty = global default)</t>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0" shapeId="0">
+      <text>
         <t>Distance from the start of the section of speed change 1, m</t>
       </text>
     </comment>
-    <comment ref="I1" authorId="0" shapeId="0">
+    <comment ref="J1" authorId="0" shapeId="0">
       <text>
         <t>New commanded speed 1, m/s</t>
       </text>
     </comment>
-    <comment ref="J1" authorId="0" shapeId="0">
+    <comment ref="K1" authorId="0" shapeId="0">
       <text>
         <t>Acceleration of change 1, m/s2 (empty = the one of the axis)</t>
       </text>
     </comment>
-    <comment ref="K1" authorId="0" shapeId="0">
+    <comment ref="L1" authorId="0" shapeId="0">
       <text>
         <t>Distance from the start of the section of speed change 2, m</t>
       </text>
     </comment>
-    <comment ref="L1" authorId="0" shapeId="0">
+    <comment ref="M1" authorId="0" shapeId="0">
       <text>
         <t>New commanded speed 2, m/s</t>
       </text>
     </comment>
-    <comment ref="M1" authorId="0" shapeId="0">
+    <comment ref="N1" authorId="0" shapeId="0">
       <text>
         <t>Acceleration of change 2, m/s2 (empty = the one of the axis)</t>
       </text>
     </comment>
-    <comment ref="N1" authorId="0" shapeId="0">
+    <comment ref="O1" authorId="0" shapeId="0">
       <text>
         <t>Distance from the start of the section of speed change 3, m</t>
       </text>
     </comment>
-    <comment ref="O1" authorId="0" shapeId="0">
+    <comment ref="P1" authorId="0" shapeId="0">
       <text>
         <t>New commanded speed 3, m/s</t>
       </text>
     </comment>
-    <comment ref="P1" authorId="0" shapeId="0">
+    <comment ref="Q1" authorId="0" shapeId="0">
       <text>
         <t>Acceleration of change 3, m/s2 (empty = the one of the axis)</t>
       </text>
     </comment>
-    <comment ref="Q1" authorId="0" shapeId="0">
+    <comment ref="R1" authorId="0" shapeId="0">
       <text>
         <t>Distance from the start of the section of speed change 4, m</t>
       </text>
     </comment>
-    <comment ref="R1" authorId="0" shapeId="0">
+    <comment ref="S1" authorId="0" shapeId="0">
       <text>
         <t>New commanded speed 4, m/s</t>
       </text>
     </comment>
-    <comment ref="S1" authorId="0" shapeId="0">
+    <comment ref="T1" authorId="0" shapeId="0">
       <text>
         <t>Acceleration of change 4, m/s2 (empty = the one of the axis)</t>
       </text>
     </comment>
-    <comment ref="T1" authorId="0" shapeId="0">
+    <comment ref="U1" authorId="0" shapeId="0">
       <text>
         <t>Distance from the start of the section of speed change 5, m</t>
       </text>
     </comment>
-    <comment ref="U1" authorId="0" shapeId="0">
+    <comment ref="V1" authorId="0" shapeId="0">
       <text>
         <t>New commanded speed 5, m/s</t>
       </text>
     </comment>
-    <comment ref="V1" authorId="0" shapeId="0">
+    <comment ref="W1" authorId="0" shapeId="0">
       <text>
         <t>Acceleration of change 5, m/s2 (empty = the one of the axis)</t>
       </text>
     </comment>
-    <comment ref="W1" authorId="0" shapeId="0">
+    <comment ref="X1" authorId="0" shapeId="0">
       <text>
         <t>Distance from the start of the section of speed change 6, m</t>
       </text>
     </comment>
-    <comment ref="X1" authorId="0" shapeId="0">
+    <comment ref="Y1" authorId="0" shapeId="0">
       <text>
         <t>New commanded speed 6, m/s</t>
       </text>
     </comment>
-    <comment ref="Y1" authorId="0" shapeId="0">
+    <comment ref="Z1" authorId="0" shapeId="0">
       <text>
         <t>Acceleration of change 6, m/s2 (empty = the one of the axis)</t>
       </text>
     </comment>
-    <comment ref="Z1" authorId="0" shapeId="0">
+    <comment ref="AA1" authorId="0" shapeId="0">
       <text>
         <t>Distance from the start of the section of speed change 7, m</t>
       </text>
     </comment>
-    <comment ref="AA1" authorId="0" shapeId="0">
+    <comment ref="AB1" authorId="0" shapeId="0">
       <text>
         <t>New commanded speed 7, m/s</t>
       </text>
     </comment>
-    <comment ref="AB1" authorId="0" shapeId="0">
+    <comment ref="AC1" authorId="0" shapeId="0">
       <text>
         <t>Acceleration of change 7, m/s2 (empty = the one of the axis)</t>
       </text>
@@ -458,17 +463,17 @@
     </comment>
     <comment ref="J1" authorId="0" shapeId="0">
       <text>
-        <t>Dead time ahead of this pass when the direction changes, s</t>
+        <t>Dead time of the reversal that FOLLOWS this pass, s</t>
       </text>
     </comment>
     <comment ref="K1" authorId="0" shapeId="0">
       <text>
-        <t>Distance between the stand and the closest extremity when the piece stops to reverse, m (empty = shortest braking distance)</t>
+        <t>Distance between the stand and the closest extremity when the piece stops for the reversal that FOLLOWS this pass, m (empty = shortest braking distance)</t>
       </text>
     </comment>
     <comment ref="L1" authorId="0" shapeId="0">
       <text>
-        <t>Approach speed after the reversal (empty = entry speed)</t>
+        <t>Speed at which the piece comes back towards THIS pass after a reversal (empty = entry speed of the pass)</t>
       </text>
     </comment>
     <comment ref="M1" authorId="0" shapeId="0">
@@ -809,7 +814,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A22"/>
+  <dimension ref="A1:A45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -869,62 +874,66 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Sections and speed events</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="60" customHeight="1">
+          <t>Sheet Layout: the kind column</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Roller tables have no setpoint of their own: the line is divided into sections defined by whoever fills in the file, possibly shorter than the spacing between two stands. Each section allows up to 7 speed changes, given as a distance from the start of the section plus a target speed.</t>
+          <t>Every row is one item of equipment placed at an absolute position. The kind column decides what the model does with it and accepts four values:</t>
         </is>
       </c>
     </row>
     <row r="12" ht="45" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>An event that would fire while a pass is engaged is deferred to disengagement, because while rolling it is the mill that commands, not the roller table. Put YES in during_pass to make it apply anyway.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>Reversing roughing</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="75" customHeight="1">
+          <t xml:space="preserve">    start    the point where the piece is released, normally the furnace exit. Exactly one row must carry it. At release the head sits here and the tail one slab length further upstream.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    stand    a rolling stand. Only these can appear in the PassSchedule sheet, and their acceleration governs the piece while it is gripped.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    coiler   the coiler. The head stops here, and the acceleration on this row is the deceleration used to bring the tail down to the final speed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>After tail-out the piece keeps going until the extremity closest to the stand is reversing_clearance_m metres away from it, where it stops, waits for the reversing delay of the following pass and restarts in the opposite direction. The reversing delay must already include screwdown and side guide centring, and the clearance is measured from the stand, so increase it if the real constraint is the edger a few metres before.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="45" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>Leaving the clearance empty makes the piece stop as soon as the deceleration allows, that is at v^2/(2a) from the stand. If the requested clearance is shorter than that distance the tool reports it rather than faking an impossible braking.</t>
-        </is>
-      </c>
+          <t xml:space="preserve">    marker   anything with no dynamics: descalers, edgers, shears. It is only drawn as a reference line on the charts and its acceleration is ignored.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>Zoom rolling</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="60" customHeight="1">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>Sheet Layout: the group column</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="90" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>It is not a comment, it drives the calculation. Stands carrying the same group label form a tandem, and inside a tandem the pass flagged as master in the PassSchedule sheet sets the mass flow: the speeds of all the other stands in the group are RECOMPUTED from it and the ones you entered are only reported as a deviation. This is deliberate, because between two stands of a tandem the strip has a fixed length, so inconsistent speeds would describe an impossible motion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="45" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Defined as a percentage speed increase starting when the head has travelled zoom_trigger_m beyond the given stand. The trigger uses the virtual head, that is it ignores the fact that the head stops at the coiler: if the trigger falls beyond the coiler the zoom starts after a few wraps, as in the offline model.</t>
+          <t>Consequence to keep in mind: emptying the group column switches that protection off without any error message, and the speeds you entered are used as they are. Same thing if the group exists but no pass in it is flagged as master.</t>
         </is>
       </c>
     </row>
@@ -934,14 +943,155 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
+          <t>Sheet Sections: speed changes</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="60" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Roller tables have no setpoint of their own: the line is divided into sections defined by whoever fills in the file, possibly shorter than the spacing between two stands. Each section allows up to 7 speed changes, given as a distance from the start of the section plus a target speed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="60" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>The distance is the point where the new speed must be REACHED, not where the ramp begins: the tool anticipates the ramp by v_new^2 - v_old^2 over twice the acceleration so that the piece is at speed exactly there. If there is not enough room the ramp starts as early as it can and the difference is reported.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="75" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>An event whose target position falls while a pass is engaged is deferred to disengagement, because while rolling it is the mill that commands and not the roller table. The same applies when a stand still to be engaged lies between the piece and the target position: a ramp cannot be planned across a pass, the bite would reset the speed anyway. Put YES in during_pass to override this.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="45" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>If instead only the anticipation reaches back into the rolling zone, while the target position is already in free running, the ramp does start during the pass and the tool reports it: it is the mill decelerating ahead of tail-out, which is a real manoeuvre.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>Accelerations: three sources, one precedence</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    1. the acceleration written next to a speed change applies to that ramp only, then the value below takes over again;</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    2. while the piece is gripped, the acceleration of the stand rolling it;</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    3. while the piece is free, the acceleration of the section it is in, or the global default table_accel_mps2 from the Simulation sheet when the section leaves it empty.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>So the braking towards a reversal and the restart afterwards use the roller table value, because in that moment the bar is moved by the table and not by the mill.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>Reversing roughing</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="75" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>The reversing delay and the reversing clearance on a row describe the reversal that FOLLOWS that pass. Reading the schedule downwards it says: finish this pass, back off by the clearance, wait for the delay, then go the other way. The last pass, and any pass followed by another one in the same direction, carry none: a value written there is ignored and reported as a warning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="90" customHeight="1">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>The clearance is the distance between the stand and the extremity of the piece closest to it once the piece has stopped, and it is measured from the stand, so increase it if the real constraint is the edger a few metres before. Leaving it empty makes the piece stop as soon as the deceleration allows, at v^2/(2a). If the requested clearance is shorter than that distance the tool reports the one actually achieved rather than faking an impossible braking.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="45" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>The approach speed instead stays on the row of the pass it belongs to: it is the speed at which the piece comes back TOWARDS that pass. So for one reversal the clearance and the delay are on one row and the approach speed on the next.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>Zoom rolling</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="75" customHeight="1">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Zoom keeps the opposite convention on purpose, the one of the offline model: zoom_trigger_m is the point where the acceleration STARTS, not where the speed is reached. It is measured from the stand on whose row it is written, and it uses the virtual head, that is it ignores the fact that the head stops at the coiler: if the trigger falls beyond the coiler the zoom starts after a few wraps.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>Arrival at the coiler</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="60" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Once the piece is free of the mill it is slowed down so that the tail reaches the coiler at coiler_v_final_mps, using the acceleration written on the coiler row of the Layout sheet. If the run-out table is too short for that deceleration, the tool reports the speed the tail actually arrives at.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
           <t>What the model does not do</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="45" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>No interlocks and no hold points: the pieces follow their nominal profiles and the tool reports where the gap drops below the threshold, without stopping the piece behind. Roller slip neglected, infinite jerk, no thermal model, no furnace or coiler cycle constraint.</t>
+    <row r="45" ht="60" customHeight="1">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>No interlocks and no hold points: the pieces follow their nominal profiles and the tool reports where the gap drops below the threshold, without stopping the piece behind. Roller slip neglected, infinite jerk, no thermal model, no coilbox, no furnace cadence constraint.</t>
         </is>
       </c>
     </row>
@@ -1080,9 +1230,6 @@
       <c r="C2" t="n">
         <v>0</v>
       </c>
-      <c r="D2" t="n">
-        <v>0.8</v>
-      </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
@@ -1104,9 +1251,6 @@
       <c r="C3" t="n">
         <v>8</v>
       </c>
-      <c r="D3" t="n">
-        <v>1</v>
-      </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
@@ -1128,9 +1272,6 @@
       <c r="C4" t="n">
         <v>22</v>
       </c>
-      <c r="D4" t="n">
-        <v>1</v>
-      </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
@@ -1176,9 +1317,6 @@
       <c r="C6" t="n">
         <v>57</v>
       </c>
-      <c r="D6" t="n">
-        <v>1</v>
-      </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
@@ -1224,9 +1362,6 @@
       <c r="C8" t="n">
         <v>175</v>
       </c>
-      <c r="D8" t="n">
-        <v>1</v>
-      </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
@@ -1248,9 +1383,6 @@
       <c r="C9" t="n">
         <v>182</v>
       </c>
-      <c r="D9" t="n">
-        <v>1</v>
-      </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
@@ -1469,7 +1601,7 @@
         <v>330</v>
       </c>
       <c r="D17" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
@@ -1490,7 +1622,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB6"/>
+  <dimension ref="A1:AC6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1500,27 +1632,28 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="15" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="15" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="15" customWidth="1" min="22" max="22"/>
-    <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="14" customWidth="1" min="24" max="24"/>
-    <col width="15" customWidth="1" min="25" max="25"/>
-    <col width="12" customWidth="1" min="26" max="26"/>
-    <col width="14" customWidth="1" min="27" max="27"/>
-    <col width="15" customWidth="1" min="28" max="28"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="15" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="15" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="15" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="25" max="25"/>
+    <col width="15" customWidth="1" min="26" max="26"/>
+    <col width="12" customWidth="1" min="27" max="27"/>
+    <col width="14" customWidth="1" min="28" max="28"/>
+    <col width="15" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -1561,105 +1694,110 @@
       </c>
       <c r="H1" s="3" t="inlineStr">
         <is>
+          <t>accel_mps2</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
           <t>d1_m</t>
         </is>
       </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>v1_mps</t>
         </is>
       </c>
-      <c r="J1" s="3" t="inlineStr">
+      <c r="K1" s="3" t="inlineStr">
         <is>
           <t>a1_mps2</t>
         </is>
       </c>
-      <c r="K1" s="3" t="inlineStr">
+      <c r="L1" s="3" t="inlineStr">
         <is>
           <t>d2_m</t>
         </is>
       </c>
-      <c r="L1" s="3" t="inlineStr">
+      <c r="M1" s="3" t="inlineStr">
         <is>
           <t>v2_mps</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
+      <c r="N1" s="3" t="inlineStr">
         <is>
           <t>a2_mps2</t>
         </is>
       </c>
-      <c r="N1" s="3" t="inlineStr">
+      <c r="O1" s="3" t="inlineStr">
         <is>
           <t>d3_m</t>
         </is>
       </c>
-      <c r="O1" s="3" t="inlineStr">
+      <c r="P1" s="3" t="inlineStr">
         <is>
           <t>v3_mps</t>
         </is>
       </c>
-      <c r="P1" s="3" t="inlineStr">
+      <c r="Q1" s="3" t="inlineStr">
         <is>
           <t>a3_mps2</t>
         </is>
       </c>
-      <c r="Q1" s="3" t="inlineStr">
+      <c r="R1" s="3" t="inlineStr">
         <is>
           <t>d4_m</t>
         </is>
       </c>
-      <c r="R1" s="3" t="inlineStr">
+      <c r="S1" s="3" t="inlineStr">
         <is>
           <t>v4_mps</t>
         </is>
       </c>
-      <c r="S1" s="3" t="inlineStr">
+      <c r="T1" s="3" t="inlineStr">
         <is>
           <t>a4_mps2</t>
         </is>
       </c>
-      <c r="T1" s="3" t="inlineStr">
+      <c r="U1" s="3" t="inlineStr">
         <is>
           <t>d5_m</t>
         </is>
       </c>
-      <c r="U1" s="3" t="inlineStr">
+      <c r="V1" s="3" t="inlineStr">
         <is>
           <t>v5_mps</t>
         </is>
       </c>
-      <c r="V1" s="3" t="inlineStr">
+      <c r="W1" s="3" t="inlineStr">
         <is>
           <t>a5_mps2</t>
         </is>
       </c>
-      <c r="W1" s="3" t="inlineStr">
+      <c r="X1" s="3" t="inlineStr">
         <is>
           <t>d6_m</t>
         </is>
       </c>
-      <c r="X1" s="3" t="inlineStr">
+      <c r="Y1" s="3" t="inlineStr">
         <is>
           <t>v6_mps</t>
         </is>
       </c>
-      <c r="Y1" s="3" t="inlineStr">
+      <c r="Z1" s="3" t="inlineStr">
         <is>
           <t>a6_mps2</t>
         </is>
       </c>
-      <c r="Z1" s="3" t="inlineStr">
+      <c r="AA1" s="3" t="inlineStr">
         <is>
           <t>d7_m</t>
         </is>
       </c>
-      <c r="AA1" s="3" t="inlineStr">
+      <c r="AB1" s="3" t="inlineStr">
         <is>
           <t>v7_mps</t>
         </is>
       </c>
-      <c r="AB1" s="3" t="inlineStr">
+      <c r="AC1" s="3" t="inlineStr">
         <is>
           <t>a7_mps2</t>
         </is>
@@ -1697,10 +1835,10 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>0</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>1.2</v>
       </c>
     </row>
@@ -1769,16 +1907,16 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="H4" t="n">
-        <v>5</v>
-      </c>
       <c r="I4" t="n">
         <v>5</v>
       </c>
-      <c r="K4" t="n">
+      <c r="J4" t="n">
+        <v>5</v>
+      </c>
+      <c r="L4" t="n">
         <v>95</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2079,7 +2217,10 @@
         <v>2.5</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>6</v>
+      </c>
+      <c r="K2" t="n">
+        <v>5</v>
       </c>
       <c r="M2" t="inlineStr"/>
     </row>
@@ -2160,10 +2301,7 @@
         <v>3.5</v>
       </c>
       <c r="J4" t="n">
-        <v>6</v>
-      </c>
-      <c r="K4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M4" t="inlineStr"/>
     </row>
@@ -2202,7 +2340,10 @@
         <v>3.5</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>6</v>
+      </c>
+      <c r="K5" t="n">
+        <v>9</v>
       </c>
       <c r="M5" t="inlineStr"/>
     </row>
@@ -2244,7 +2385,7 @@
         <v>6</v>
       </c>
       <c r="K6" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="M6" t="inlineStr"/>
     </row>
@@ -2283,10 +2424,7 @@
         <v>4.5</v>
       </c>
       <c r="J7" t="n">
-        <v>6</v>
-      </c>
-      <c r="K7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M7" t="inlineStr"/>
     </row>
@@ -2585,7 +2723,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2791,30 +2929,60 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>max_time_s</t>
+          <t>table_accel_mps2</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1800</v>
+        <v>1</v>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Maximum simulation time of a single piece, s</t>
+          <t>Default roller table acceleration, m/s2</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>coiler_v_final_mps</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Speed the tail must have when it reaches the coiler, m/s</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>max_time_s</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1800</v>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Maximum simulation time of a single piece, s</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>time_axis_down</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>YES for time increasing downwards on the diagram</t>
         </is>

--- a/examples/hsm_example.xlsx
+++ b/examples/hsm_example.xlsx
@@ -2300,9 +2300,6 @@
       <c r="I4" t="n">
         <v>3.5</v>
       </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
       <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
@@ -2423,9 +2420,6 @@
       <c r="I7" t="n">
         <v>4.5</v>
       </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
       <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
@@ -2462,9 +2456,6 @@
       <c r="I8" t="n">
         <v>1.7</v>
       </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
       <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
@@ -2501,9 +2492,6 @@
       <c r="I9" t="n">
         <v>2.84</v>
       </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
       <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
@@ -2540,9 +2528,6 @@
       <c r="I10" t="n">
         <v>4.36</v>
       </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
       <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
@@ -2579,9 +2564,6 @@
       <c r="I11" t="n">
         <v>6.25</v>
       </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
       <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
@@ -2618,9 +2600,6 @@
       <c r="I12" t="n">
         <v>8.33</v>
       </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
       <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
@@ -2657,9 +2636,6 @@
       <c r="I13" t="n">
         <v>10.42</v>
       </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
       <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
@@ -2695,9 +2671,6 @@
       </c>
       <c r="I14" t="n">
         <v>12.5</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
